--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB497D1-2EB7-492C-9F65-C4C896F075B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CC96F8-3188-4605-AFAA-8507CDAFB3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -1379,187 +1379,187 @@
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 1</t>
+    <t>wind offshore electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>elc_wof_002</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 2</t>
+    <t>wind offshore electricity generation in cluster -- 2</t>
   </si>
   <si>
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 3</t>
+    <t>wind offshore electricity generation in cluster -- 3</t>
   </si>
   <si>
     <t>elc_wof_004</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 4</t>
+    <t>wind offshore electricity generation in cluster -- 4</t>
   </si>
   <si>
     <t>elc_wof_005</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 5</t>
+    <t>wind offshore electricity generation in cluster -- 5</t>
   </si>
   <si>
     <t>elc_wof_006</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 6</t>
+    <t>wind offshore electricity generation in cluster -- 6</t>
   </si>
   <si>
     <t>elc_wof_007</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 7</t>
+    <t>wind offshore electricity generation in cluster -- 7</t>
   </si>
   <si>
     <t>elc_wof_008</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 8</t>
+    <t>wind offshore electricity generation in cluster -- 8</t>
   </si>
   <si>
     <t>elc_wof_009</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 9</t>
+    <t>wind offshore electricity generation in cluster -- 9</t>
   </si>
   <si>
     <t>elc_wof_010</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 10</t>
+    <t>wind offshore electricity generation in cluster -- 10</t>
   </si>
   <si>
     <t>elc_wof_011</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 11</t>
+    <t>wind offshore electricity generation in cluster -- 11</t>
   </si>
   <si>
     <t>elc_wof_012</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 12</t>
+    <t>wind offshore electricity generation in cluster -- 12</t>
   </si>
   <si>
     <t>elc_wof_013</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 13</t>
+    <t>wind offshore electricity generation in cluster -- 13</t>
   </si>
   <si>
     <t>elc_wof_014</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 14</t>
+    <t>wind offshore electricity generation in cluster -- 14</t>
   </si>
   <si>
     <t>elc_wof_015</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 15</t>
+    <t>wind offshore electricity generation in cluster -- 15</t>
   </si>
   <si>
     <t>elc_wof_016</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 16</t>
+    <t>wind offshore electricity generation in cluster -- 16</t>
   </si>
   <si>
     <t>elc_wof_017</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 17</t>
+    <t>wind offshore electricity generation in cluster -- 17</t>
   </si>
   <si>
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 18</t>
+    <t>wind offshore electricity generation in cluster -- 18</t>
   </si>
   <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 19</t>
+    <t>wind offshore electricity generation in cluster -- 19</t>
   </si>
   <si>
     <t>elc_wof_020</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 20</t>
+    <t>wind offshore electricity generation in cluster -- 20</t>
   </si>
   <si>
     <t>elc_wof_021</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 21</t>
+    <t>wind offshore electricity generation in cluster -- 21</t>
   </si>
   <si>
     <t>elc_wof_022</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 22</t>
+    <t>wind offshore electricity generation in cluster -- 22</t>
   </si>
   <si>
     <t>elc_wof_023</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 23</t>
+    <t>wind offshore electricity generation in cluster -- 23</t>
   </si>
   <si>
     <t>elc_wof_024</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 24</t>
+    <t>wind offshore electricity generation in cluster -- 24</t>
   </si>
   <si>
     <t>elc_wof_025</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 25</t>
+    <t>wind offshore electricity generation in cluster -- 25</t>
   </si>
   <si>
     <t>elc_wof_026</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 26</t>
+    <t>wind offshore electricity generation in cluster -- 26</t>
   </si>
   <si>
     <t>elc_wof_027</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 27</t>
+    <t>wind offshore electricity generation in cluster -- 27</t>
   </si>
   <si>
     <t>elc_wof_028</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 28</t>
+    <t>wind offshore electricity generation in cluster -- 28</t>
   </si>
   <si>
     <t>elc_wof_029</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 29</t>
+    <t>wind offshore electricity generation in cluster -- 29</t>
   </si>
   <si>
     <t>elc_wof_030</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 30</t>
+    <t>wind offshore electricity generation in cluster -- 30</t>
   </si>
   <si>
     <t>elc_wof_031</t>
   </si>
   <si>
-    <t>offwind electricity generation in cluster -- 31</t>
+    <t>wind offshore electricity generation in cluster -- 31</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1D0CE7-08DA-4BD0-B53D-05D771F7BCBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB34507-2EC0-4961-A546-CE22369730D8}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CC96F8-3188-4605-AFAA-8507CDAFB3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9389B3-58DC-4A4F-BFF5-E15ED4448EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB34507-2EC0-4961-A546-CE22369730D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8770CF65-97BF-4B7F-A502-816BB6A70E14}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9389B3-58DC-4A4F-BFF5-E15ED4448EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6EED8B-1EA4-420D-8144-5E21E4ACF725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8770CF65-97BF-4B7F-A502-816BB6A70E14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4AE7B45-46D3-43E3-939B-8B78FB146774}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6EED8B-1EA4-420D-8144-5E21E4ACF725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25831DC3-8754-44CF-A164-01F057241131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4AE7B45-46D3-43E3-939B-8B78FB146774}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A0E44B-DA4F-4B8D-A9B6-066E2DDA3260}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25831DC3-8754-44CF-A164-01F057241131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8265F3-E2FC-44E7-AFE6-9201171F05C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A0E44B-DA4F-4B8D-A9B6-066E2DDA3260}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CD21E5-FE74-4173-8C22-C29B5A7DE078}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8265F3-E2FC-44E7-AFE6-9201171F05C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E331997E-DA15-4CEB-968A-C0EB0EBFF7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CD21E5-FE74-4173-8C22-C29B5A7DE078}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8943F0-98F5-493E-9201-4B4C2063C47C}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E331997E-DA15-4CEB-968A-C0EB0EBFF7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201197D0-7D7C-480A-8A29-142350403806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8943F0-98F5-493E-9201-4B4C2063C47C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC4CE15-CC85-4DA8-8B5B-1CE90A5F587A}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201197D0-7D7C-480A-8A29-142350403806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC526B7-4992-4B58-9564-0F044246EBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC4CE15-CC85-4DA8-8B5B-1CE90A5F587A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327A569B-CC5E-4413-B845-667D153651DF}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC526B7-4992-4B58-9564-0F044246EBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF25477C-3E3B-472E-895D-0834F219C7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327A569B-CC5E-4413-B845-667D153651DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19774576-5F2B-4EAF-8A74-5CEF07506F64}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF25477C-3E3B-472E-895D-0834F219C7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA506B15-7FD3-418D-9F46-837D6FA07EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19774576-5F2B-4EAF-8A74-5CEF07506F64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE15938-DDD2-48AA-ABC9-C0ECA69955B7}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA506B15-7FD3-418D-9F46-837D6FA07EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD026921-5313-41FF-B1C1-78AEC5BC3BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CE15938-DDD2-48AA-ABC9-C0ECA69955B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B331CA-A3FB-4297-BD80-CF163FC4F0AF}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD026921-5313-41FF-B1C1-78AEC5BC3BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE7EC7-6A9B-4094-B26C-85CEC386860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B331CA-A3FB-4297-BD80-CF163FC4F0AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E797F95-3F26-4868-968F-BB5AE22676F4}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE7EC7-6A9B-4094-B26C-85CEC386860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2BB96F-B14D-46FC-8BC9-B1D69B23F8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E797F95-3F26-4868-968F-BB5AE22676F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AC0192-1C4A-4F5B-9C8F-34A7ACB56867}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2BB96F-B14D-46FC-8BC9-B1D69B23F8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B89C0D-BA73-411E-BC78-C68D668A845B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AC0192-1C4A-4F5B-9C8F-34A7ACB56867}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956A3DB9-633D-4820-953C-9718A21B44BC}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B89C0D-BA73-411E-BC78-C68D668A845B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE4A237-4B46-4102-9B57-853668B75EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956A3DB9-633D-4820-953C-9718A21B44BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95DFC1E-0A22-4F35-8603-36EAED2FA487}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE4A237-4B46-4102-9B57-853668B75EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19850957-3D5E-48F6-A5E1-D8C17C080E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95DFC1E-0A22-4F35-8603-36EAED2FA487}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BA7F62-0571-4A00-A850-938CA6C8C1B2}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19850957-3D5E-48F6-A5E1-D8C17C080E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E9A948-BD49-4C7A-8D4A-335234C17337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BA7F62-0571-4A00-A850-938CA6C8C1B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7D32E5-B048-4D28-BE16-C2608A7F478A}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E9A948-BD49-4C7A-8D4A-335234C17337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B862F2B-A6B1-40EA-8624-55F239AE9A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7D32E5-B048-4D28-BE16-C2608A7F478A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4B33B9-62FE-40AB-B551-B48D3D1F60DE}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B862F2B-A6B1-40EA-8624-55F239AE9A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602BE0FE-305B-44B6-A797-B30F61311EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4B33B9-62FE-40AB-B551-B48D3D1F60DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68ACFD87-BD4E-4A85-8519-FAD2EC6DABB1}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602BE0FE-305B-44B6-A797-B30F61311EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B4C082-7248-456F-86E5-1376A1954C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68ACFD87-BD4E-4A85-8519-FAD2EC6DABB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551E5552-B6BC-474A-85FE-C76ECD52B9F0}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B4C082-7248-456F-86E5-1376A1954C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F436A63-9FAB-4BF4-8B19-22B961504275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6446,7 +6446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551E5552-B6BC-474A-85FE-C76ECD52B9F0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59DFDBDE-F09E-49CC-975D-74892E1DD516}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F436A63-9FAB-4BF4-8B19-22B961504275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE5C9A4-3ABB-4AE1-9C85-833112AB3FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4244" uniqueCount="1331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4245" uniqueCount="1332">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -4032,6 +4032,9 @@
   </si>
   <si>
     <t>grid node -- way/969586211-525</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
   </si>
 </sst>
 </file>
@@ -19379,6 +19382,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
     <row r="13" spans="2:12">
       <c r="B13" s="14" t="s">
         <v>63</v>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7278C956-5D08-4BCB-87D3-5366A88F05E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F4F170-3B90-4CB2-87EC-6377E93A8421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -11335,7 +11335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB352BB-0238-407E-BB0F-0E3206181DDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DECE0F-5D15-4052-8582-899777069DB0}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F4F170-3B90-4CB2-87EC-6377E93A8421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B7B6A4-804E-452D-BFBB-1331E03055CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11335,7 +11335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30DECE0F-5D15-4052-8582-899777069DB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583E203F-34FB-4F91-93F1-B5D871B10282}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SysSettings.xlsx
+++ b/VerveStacks_BRA_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B7B6A4-804E-452D-BFBB-1331E03055CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E348FB9-7DA2-467F-9470-6844A8441E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11335,7 +11335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583E203F-34FB-4F91-93F1-B5D871B10282}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A42F66-0EF4-4E1D-8880-E7F3CFE71F3E}">
   <dimension ref="B3:H346"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
